--- a/images/20220127/运维领域模型.xlsx
+++ b/images/20220127/运维领域模型.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="15640" tabRatio="917" activeTab="10"/>
+    <workbookView windowWidth="29400" windowHeight="15640" tabRatio="917" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="运维阶段" sheetId="2" r:id="rId1"/>
@@ -2219,6 +2219,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="DengXian (正文)"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
@@ -2228,12 +2234,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="DengXian (正文)"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="5"/>
       <name val="DengXian (正文)"/>
       <charset val="134"/>
     </font>

--- a/images/20220127/运维领域模型.xlsx
+++ b/images/20220127/运维领域模型.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="15640" tabRatio="917" activeTab="6"/>
+    <workbookView windowWidth="29400" windowHeight="14120" tabRatio="917" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="运维阶段" sheetId="2" r:id="rId1"/>
@@ -1809,6 +1809,9 @@
     <t>运维中台</t>
   </si>
   <si>
+    <t>IAM：身份，权限</t>
+  </si>
+  <si>
     <t>成本：计量、计费，对账，分摊、预算，报表</t>
   </si>
   <si>
@@ -1816,9 +1819,6 @@
   </si>
   <si>
     <t>变更：编排、管控CM/决策、执行,工单、作业、CD、预案</t>
-  </si>
-  <si>
-    <t>IAM：身份，权限</t>
   </si>
   <si>
     <t>元数据：CMDB、ZNS，IPS</t>
@@ -2219,12 +2219,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="5"/>
-      <name val="DengXian (正文)"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
@@ -2234,6 +2228,12 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="DengXian (正文)"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="5"/>
       <name val="DengXian (正文)"/>
       <charset val="134"/>
     </font>
